--- a/erp-server/erp-server-wms/src/main/resources/excel/virtualTransFlow.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/virtualTransFlow.xlsx
@@ -1046,16 +1046,17 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="2" max="2" width="12.875" customWidth="1"/>
-    <col min="3" max="3" width="11.625" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="1" max="1" width="18.5" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16.875" customWidth="1"/>
+    <col min="4" max="4" width="14.125" customWidth="1"/>
     <col min="5" max="5" width="11.5" customWidth="1"/>
-    <col min="6" max="7" width="11.25" customWidth="1"/>
+    <col min="6" max="6" width="18.25" customWidth="1"/>
+    <col min="7" max="7" width="18.625" customWidth="1"/>
     <col min="8" max="8" width="16.125" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="14.625" customWidth="1"/>
-    <col min="11" max="11" width="11.5" customWidth="1"/>
+    <col min="11" max="11" width="18.25" customWidth="1"/>
     <col min="12" max="12" width="15.75" customWidth="1"/>
     <col min="13" max="13" width="12.125" customWidth="1"/>
     <col min="14" max="14" width="14.125" customWidth="1"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/virtualTransFlow.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/virtualTransFlow.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1050,7 +1048,7 @@
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="16.875" customWidth="1"/>
     <col min="4" max="4" width="14.125" customWidth="1"/>
-    <col min="5" max="5" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="18.625" customWidth="1"/>
     <col min="6" max="6" width="18.25" customWidth="1"/>
     <col min="7" max="7" width="18.625" customWidth="1"/>
     <col min="8" max="8" width="16.125" customWidth="1"/>
@@ -1155,28 +1153,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-wms/src/main/resources/excel/virtualTransFlow.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/virtualTransFlow.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>流水号</t>
   </si>
@@ -35,6 +35,9 @@
     <t>出入库时间</t>
   </si>
   <si>
+    <t>业务日期</t>
+  </si>
+  <si>
     <t>单据类型</t>
   </si>
   <si>
@@ -75,6 +78,9 @@
   </si>
   <si>
     <t>{.tradeTime}</t>
+  </si>
+  <si>
+    <t>{.billDate}</t>
   </si>
   <si>
     <t>{.sourceTypeName}</t>
@@ -1041,26 +1047,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="16.875" customWidth="1"/>
-    <col min="4" max="4" width="14.125" customWidth="1"/>
-    <col min="5" max="5" width="18.625" customWidth="1"/>
-    <col min="6" max="6" width="18.25" customWidth="1"/>
-    <col min="7" max="7" width="18.625" customWidth="1"/>
-    <col min="8" max="8" width="16.125" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="14.625" customWidth="1"/>
-    <col min="11" max="11" width="18.25" customWidth="1"/>
-    <col min="12" max="12" width="15.75" customWidth="1"/>
-    <col min="13" max="13" width="12.125" customWidth="1"/>
-    <col min="14" max="14" width="14.125" customWidth="1"/>
+    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16.875" customWidth="1"/>
+    <col min="5" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="18.625" customWidth="1"/>
+    <col min="7" max="7" width="18.25" customWidth="1"/>
+    <col min="8" max="8" width="18.625" customWidth="1"/>
+    <col min="9" max="9" width="16.125" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="14.625" customWidth="1"/>
+    <col min="12" max="12" width="18.25" customWidth="1"/>
+    <col min="13" max="13" width="15.75" customWidth="1"/>
+    <col min="14" max="14" width="12.125" customWidth="1"/>
+    <col min="15" max="15" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1103,49 +1109,55 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
